--- a/02_clean_data/40_09_models3_excel.xlsx
+++ b/02_clean_data/40_09_models3_excel.xlsx
@@ -1,18 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <workbookPr date1904="false"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <workbookPr defaultThemeVersion="166925"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\recup\Desktop\TESIS\PAPERS\01_INDIVIDUO\git_repo\Tesis_Individuo\02_clean_data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D58CB209-D80F-4C00-B6CC-ED2354EC690C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView activeTab="0"/>
+    <workbookView xWindow="168" yWindow="0" windowWidth="11412" windowHeight="12360" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" r:id="rId3" sheetId="1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="58">
   <si>
     <t>variable</t>
   </si>
@@ -177,16 +185,35 @@
   </si>
   <si>
     <t>Rs17</t>
+  </si>
+  <si>
+    <t>*</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Ok</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+  </numFmts>
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
-      <sz val="11.0"/>
+      <sz val="11"/>
+      <color indexed="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color indexed="8"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -198,7 +225,7 @@
       <patternFill patternType="none"/>
     </fill>
     <fill>
-      <patternFill patternType="darkGray"/>
+      <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="1">
@@ -213,19 +240,329 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="165" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
+  <cellStyles count="1">
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+  </cellStyles>
+  <dxfs count="0"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
+<file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+  <a:themeElements>
+    <a:clrScheme name="Office">
+      <a:dk1>
+        <a:sysClr val="windowText" lastClr="000000"/>
+      </a:dk1>
+      <a:lt1>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
+      </a:lt1>
+      <a:dk2>
+        <a:srgbClr val="44546A"/>
+      </a:dk2>
+      <a:lt2>
+        <a:srgbClr val="E7E6E6"/>
+      </a:lt2>
+      <a:accent1>
+        <a:srgbClr val="4472C4"/>
+      </a:accent1>
+      <a:accent2>
+        <a:srgbClr val="ED7D31"/>
+      </a:accent2>
+      <a:accent3>
+        <a:srgbClr val="A5A5A5"/>
+      </a:accent3>
+      <a:accent4>
+        <a:srgbClr val="FFC000"/>
+      </a:accent4>
+      <a:accent5>
+        <a:srgbClr val="5B9BD5"/>
+      </a:accent5>
+      <a:accent6>
+        <a:srgbClr val="70AD47"/>
+      </a:accent6>
+      <a:hlink>
+        <a:srgbClr val="0563C1"/>
+      </a:hlink>
+      <a:folHlink>
+        <a:srgbClr val="954F72"/>
+      </a:folHlink>
+    </a:clrScheme>
+    <a:fontScheme name="Office">
+      <a:majorFont>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:majorFont>
+      <a:minorFont>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:ea typeface=""/>
+        <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
+        <a:font script="Armn" typeface="Arial"/>
+        <a:font script="Bugi" typeface="Leelawadee UI"/>
+        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
+        <a:font script="Java" typeface="Javanese Text"/>
+        <a:font script="Lisu" typeface="Segoe UI"/>
+        <a:font script="Mymr" typeface="Myanmar Text"/>
+        <a:font script="Nkoo" typeface="Ebrima"/>
+        <a:font script="Olck" typeface="Nirmala UI"/>
+        <a:font script="Osma" typeface="Ebrima"/>
+        <a:font script="Phag" typeface="Phagspa"/>
+        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
+        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
+        <a:font script="Syre" typeface="Estrangelo Edessa"/>
+        <a:font script="Sora" typeface="Nirmala UI"/>
+        <a:font script="Tale" typeface="Microsoft Tai Le"/>
+        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
+        <a:font script="Tfng" typeface="Ebrima"/>
+      </a:minorFont>
+    </a:fontScheme>
+    <a:fmtScheme name="Office">
+      <a:fillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="110000"/>
+                <a:satMod val="105000"/>
+                <a:tint val="67000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="103000"/>
+                <a:tint val="73000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="105000"/>
+                <a:satMod val="109000"/>
+                <a:tint val="81000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:satMod val="103000"/>
+                <a:lumMod val="102000"/>
+                <a:tint val="94000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:satMod val="110000"/>
+                <a:lumMod val="100000"/>
+                <a:shade val="100000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:lumMod val="99000"/>
+                <a:satMod val="120000"/>
+                <a:shade val="78000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:fillStyleLst>
+      <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
+      </a:lnStyleLst>
+      <a:effectStyleLst>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst/>
+        </a:effectStyle>
+        <a:effectStyle>
+          <a:effectLst>
+            <a:outerShdw blurRad="57150" dist="19050" dir="5400000" algn="ctr" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="63000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+        </a:effectStyle>
+      </a:effectStyleLst>
+      <a:bgFillStyleLst>
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:solidFill>
+          <a:schemeClr val="phClr">
+            <a:tint val="95000"/>
+            <a:satMod val="170000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:gradFill rotWithShape="1">
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="93000"/>
+                <a:satMod val="150000"/>
+                <a:shade val="98000"/>
+                <a:lumMod val="102000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="50000">
+              <a:schemeClr val="phClr">
+                <a:tint val="98000"/>
+                <a:satMod val="130000"/>
+                <a:shade val="90000"/>
+                <a:lumMod val="103000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="63000"/>
+                <a:satMod val="120000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:lin ang="5400000" scaled="0"/>
+        </a:gradFill>
+      </a:bgFillStyleLst>
+    </a:fmtScheme>
+  </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
+  <a:extLst>
+    <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+    </a:ext>
+  </a:extLst>
+</a:theme>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:H26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1">
-      <c r="A1"/>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -242,507 +579,547 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
       <c r="B2" t="s">
         <v>30</v>
       </c>
-      <c r="C2" t="n">
-        <v>0.0170512571494758</v>
-      </c>
-      <c r="D2" t="n">
-        <v>0.00200315227458537</v>
-      </c>
-      <c r="E2" t="n">
-        <v>0.175361143349565</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.271864066791298</v>
-      </c>
-    </row>
-    <row r="3">
+      <c r="C2" s="1">
+        <v>1.70512571494758E-2</v>
+      </c>
+      <c r="D2" s="1">
+        <v>2.0031522745853699E-3</v>
+      </c>
+      <c r="E2" s="2">
+        <v>0.17536114334956501</v>
+      </c>
+      <c r="F2" s="2">
+        <v>0.27186406679129799</v>
+      </c>
+      <c r="G2" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
       <c r="B3" t="s">
         <v>31</v>
       </c>
-      <c r="C3" t="n">
-        <v>0.054576371404093</v>
-      </c>
-      <c r="D3" t="n">
-        <v>0.0166584452375049</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.908184775309227</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.170926784742636</v>
-      </c>
-    </row>
-    <row r="4">
+      <c r="C3" s="2">
+        <v>5.4576371404093001E-2</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1.6658445237504899E-2</v>
+      </c>
+      <c r="E3" s="2">
+        <v>0.90818477530922703</v>
+      </c>
+      <c r="F3" s="2">
+        <v>0.17092678474263601</v>
+      </c>
+      <c r="G3" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>32</v>
       </c>
-      <c r="C4" t="n">
-        <v>0.758041568218259</v>
-      </c>
-      <c r="D4" t="n">
-        <v>0.481773699029709</v>
-      </c>
-      <c r="E4" t="n">
-        <v>0.144243146018756</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.387692061412964</v>
-      </c>
-    </row>
-    <row r="5">
+      <c r="C4" s="2">
+        <v>0.75804156821825897</v>
+      </c>
+      <c r="D4" s="2">
+        <v>0.48177369902970901</v>
+      </c>
+      <c r="E4" s="2">
+        <v>0.14424314601875601</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.38769206141296397</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>33</v>
       </c>
-      <c r="C5" t="n">
-        <v>0.0432379618904949</v>
-      </c>
-      <c r="D5" t="n">
-        <v>0.338963694525125</v>
-      </c>
-      <c r="E5" t="n">
-        <v>0.0549362999605156</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.3310312185986</v>
-      </c>
-    </row>
-    <row r="6">
+      <c r="C5" s="1">
+        <v>4.3237961890494898E-2</v>
+      </c>
+      <c r="D5" s="2">
+        <v>0.33896369452512498</v>
+      </c>
+      <c r="E5" s="2">
+        <v>5.4936299960515599E-2</v>
+      </c>
+      <c r="F5" s="2">
+        <v>0.33103121859860002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>34</v>
       </c>
-      <c r="C6" t="n">
-        <v>0.568750820144962</v>
-      </c>
-      <c r="D6" t="n">
-        <v>0.482021580240042</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.913022930804366</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.730672476577158</v>
-      </c>
-    </row>
-    <row r="7">
+      <c r="C6" s="2">
+        <v>0.56875082014496203</v>
+      </c>
+      <c r="D6" s="2">
+        <v>0.48202158024004199</v>
+      </c>
+      <c r="E6" s="2">
+        <v>0.91302293080436603</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0.73067247657715795</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>35</v>
       </c>
-      <c r="C7" t="n">
-        <v>0.745165563984755</v>
-      </c>
-      <c r="D7" t="n">
-        <v>0.32634714794022</v>
-      </c>
-      <c r="E7" t="n">
-        <v>0.758646996993874</v>
-      </c>
-      <c r="F7" t="n">
+      <c r="C7" s="2">
+        <v>0.74516556398475498</v>
+      </c>
+      <c r="D7" s="2">
+        <v>0.32634714794022002</v>
+      </c>
+      <c r="E7" s="2">
+        <v>0.75864699699387395</v>
+      </c>
+      <c r="F7" s="2">
         <v>0.217977743728068</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>36</v>
       </c>
-      <c r="C8" t="n">
-        <v>0.21413824669079</v>
-      </c>
-      <c r="D8" t="n">
-        <v>0.54588860283111</v>
-      </c>
-      <c r="E8" t="n">
-        <v>0.960566014655495</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.250848291144727</v>
-      </c>
-    </row>
-    <row r="9">
+      <c r="C8" s="2">
+        <v>0.21413824669079001</v>
+      </c>
+      <c r="D8" s="2">
+        <v>0.54588860283110996</v>
+      </c>
+      <c r="E8" s="2">
+        <v>0.96056601465549496</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.25084829114472701</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
       <c r="B9" t="s">
         <v>37</v>
       </c>
-      <c r="C9" t="n">
-        <v>0.97397030492523</v>
-      </c>
-      <c r="D9" t="n">
+      <c r="C9" s="2">
+        <v>0.97397030492522996</v>
+      </c>
+      <c r="D9" s="2">
         <v>0.102614825486774</v>
       </c>
-      <c r="E9" t="n">
-        <v>0.596101980940747</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.415338412948782</v>
-      </c>
-    </row>
-    <row r="10">
+      <c r="E9" s="2">
+        <v>0.59610198094074696</v>
+      </c>
+      <c r="F9" s="2">
+        <v>0.41533841294878199</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
       <c r="B10" t="s">
         <v>38</v>
       </c>
-      <c r="C10" t="n">
-        <v>0.00192631120298784</v>
-      </c>
-      <c r="D10" t="n">
-        <v>0.00135906652948661</v>
-      </c>
-      <c r="E10" t="n">
+      <c r="C10" s="1">
+        <v>1.9263112029878401E-3</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1.3590665294866101E-3</v>
+      </c>
+      <c r="E10" s="2">
         <v>0.131924568663249</v>
       </c>
-      <c r="F10" t="n">
+      <c r="F10" s="2">
         <v>0.270258503136379</v>
       </c>
-    </row>
-    <row r="11">
+      <c r="G10" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
       <c r="B11" t="s">
         <v>39</v>
       </c>
-      <c r="C11" t="n">
-        <v>0.00269094248351097</v>
-      </c>
-      <c r="D11" t="n">
+      <c r="C11" s="1">
+        <v>2.69094248351097E-3</v>
+      </c>
+      <c r="D11" s="2">
         <v>0.249324809379081</v>
       </c>
-      <c r="E11" t="n">
-        <v>0.00723544895891182</v>
-      </c>
-      <c r="F11" t="n">
-        <v>0.0048855514164263</v>
-      </c>
-    </row>
-    <row r="12">
+      <c r="E11" s="1">
+        <v>7.23544895891182E-3</v>
+      </c>
+      <c r="F11" s="1">
+        <v>4.8855514164262998E-3</v>
+      </c>
+      <c r="G11" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
       <c r="B12" t="s">
         <v>40</v>
       </c>
-      <c r="C12" t="n">
-        <v>0.0226624403685616</v>
-      </c>
-      <c r="D12" t="n">
-        <v>0.949617901387124</v>
-      </c>
-      <c r="E12" t="n">
-        <v>0.0408354142761522</v>
-      </c>
-      <c r="F12" t="n">
-        <v>0.00394817283411202</v>
-      </c>
-    </row>
-    <row r="13">
+      <c r="C12" s="1">
+        <v>2.26624403685616E-2</v>
+      </c>
+      <c r="D12" s="2">
+        <v>0.94961790138712399</v>
+      </c>
+      <c r="E12" s="1">
+        <v>4.0835414276152199E-2</v>
+      </c>
+      <c r="F12" s="1">
+        <v>3.9481728341120197E-3</v>
+      </c>
+      <c r="G12" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
       <c r="B13" t="s">
         <v>41</v>
       </c>
-      <c r="C13" t="n">
-        <v>0.00430059343320842</v>
-      </c>
-      <c r="D13" t="n">
+      <c r="C13" s="1">
+        <v>4.3005934332084198E-3</v>
+      </c>
+      <c r="D13" s="2">
         <v>0.392804218678801</v>
       </c>
-      <c r="E13" t="n">
-        <v>0.0109968795160923</v>
-      </c>
-      <c r="F13" t="n">
-        <v>0.00416435857594567</v>
-      </c>
-    </row>
-    <row r="14">
+      <c r="E13" s="1">
+        <v>1.09968795160923E-2</v>
+      </c>
+      <c r="F13" s="1">
+        <v>4.1643585759456696E-3</v>
+      </c>
+      <c r="G13" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
       <c r="B14" t="s">
         <v>42</v>
       </c>
-      <c r="C14" t="n">
-        <v>0.0580490148718599</v>
-      </c>
-      <c r="D14" t="n">
-        <v>0.977144655052753</v>
-      </c>
-      <c r="E14" t="n">
-        <v>0.0646130037692294</v>
-      </c>
-      <c r="F14" t="n">
-        <v>0.0387742225395996</v>
-      </c>
-    </row>
-    <row r="15">
+      <c r="C14" s="2">
+        <v>5.80490148718599E-2</v>
+      </c>
+      <c r="D14" s="2">
+        <v>0.97714465505275305</v>
+      </c>
+      <c r="E14" s="2">
+        <v>6.4613003769229405E-2</v>
+      </c>
+      <c r="F14" s="1">
+        <v>3.8774222539599598E-2</v>
+      </c>
+      <c r="G14" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
       <c r="B15" t="s">
         <v>43</v>
       </c>
-      <c r="C15" t="n">
-        <v>0.0371922728956547</v>
-      </c>
-      <c r="D15" t="n">
-        <v>0.0617393380204791</v>
-      </c>
-      <c r="E15" t="n">
-        <v>0.0546409636785924</v>
-      </c>
-      <c r="F15" t="n">
-        <v>0.162365873936314</v>
-      </c>
-    </row>
-    <row r="16">
+      <c r="C15" s="1">
+        <v>3.7192272895654702E-2</v>
+      </c>
+      <c r="D15" s="2">
+        <v>6.1739338020479102E-2</v>
+      </c>
+      <c r="E15" s="2">
+        <v>5.4640963678592398E-2</v>
+      </c>
+      <c r="F15" s="2">
+        <v>0.16236587393631399</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>19</v>
       </c>
       <c r="B16" t="s">
         <v>44</v>
       </c>
-      <c r="C16" t="n">
-        <v>8.54162106709144E-4</v>
-      </c>
-      <c r="D16" t="n">
-        <v>0.0837280111212787</v>
-      </c>
-      <c r="E16" t="n">
-        <v>0.0308379508209868</v>
-      </c>
-      <c r="F16" t="n">
+      <c r="C16" s="1">
+        <v>8.5416210670914402E-4</v>
+      </c>
+      <c r="D16" s="2">
+        <v>8.37280111212787E-2</v>
+      </c>
+      <c r="E16" s="1">
+        <v>3.0837950820986799E-2</v>
+      </c>
+      <c r="F16" s="1">
         <v>9.62127868727706E-4</v>
       </c>
-    </row>
-    <row r="17">
+      <c r="G16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
       <c r="B17" t="s">
         <v>45</v>
       </c>
-      <c r="C17" t="n">
-        <v>0.287746741434538</v>
-      </c>
-      <c r="D17" t="n">
-        <v>0.340686979470153</v>
-      </c>
-      <c r="E17" t="n">
+      <c r="C17" s="2">
+        <v>0.28774674143453799</v>
+      </c>
+      <c r="D17" s="2">
+        <v>0.34068697947015297</v>
+      </c>
+      <c r="E17" s="2">
         <v>0.602763427911997</v>
       </c>
-      <c r="F17" t="n">
-        <v>0.0683238537910247</v>
-      </c>
-    </row>
-    <row r="18">
+      <c r="F17" s="2">
+        <v>6.8323853791024694E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>21</v>
       </c>
       <c r="B18" t="s">
         <v>46</v>
       </c>
-      <c r="C18" t="n">
+      <c r="C18" s="2">
         <v>0.115914681765412</v>
       </c>
-      <c r="D18" t="n">
-        <v>0.842415545793489</v>
-      </c>
-      <c r="E18" t="n">
-        <v>0.721256924079494</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.0734884639620042</v>
-      </c>
-    </row>
-    <row r="19">
+      <c r="D18" s="2">
+        <v>0.84241554579348898</v>
+      </c>
+      <c r="E18" s="2">
+        <v>0.72125692407949404</v>
+      </c>
+      <c r="F18" s="2">
+        <v>7.3488463962004202E-2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>22</v>
       </c>
       <c r="B19" t="s">
         <v>47</v>
       </c>
-      <c r="C19" t="n">
-        <v>0.548987739109401</v>
-      </c>
-      <c r="D19" t="n">
-        <v>0.63400085714778</v>
-      </c>
-      <c r="E19" t="n">
-        <v>0.82433011035275</v>
-      </c>
-      <c r="F19" t="n">
+      <c r="C19" s="2">
+        <v>0.54898773910940102</v>
+      </c>
+      <c r="D19" s="2">
+        <v>0.63400085714777998</v>
+      </c>
+      <c r="E19" s="2">
+        <v>0.82433011035274995</v>
+      </c>
+      <c r="F19" s="2">
         <v>0.276096975191015</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>23</v>
       </c>
       <c r="B20" t="s">
         <v>48</v>
       </c>
-      <c r="C20" t="n">
+      <c r="C20" s="2">
         <v>0.484003663543979</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.173425108191983</v>
-      </c>
-      <c r="E20" t="n">
-        <v>0.0528044572456518</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.970668714180292</v>
-      </c>
-    </row>
-    <row r="21">
+      <c r="D20" s="2">
+        <v>0.17342510819198301</v>
+      </c>
+      <c r="E20" s="2">
+        <v>5.2804457245651797E-2</v>
+      </c>
+      <c r="F20" s="2">
+        <v>0.97066871418029199</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>24</v>
       </c>
       <c r="B21" t="s">
         <v>49</v>
       </c>
-      <c r="C21" t="n">
-        <v>1.8135352581153E-6</v>
-      </c>
-      <c r="D21" t="n">
-        <v>0.407239051031684</v>
-      </c>
-      <c r="E21" t="n">
-        <v>1.73575963960607E-4</v>
-      </c>
-      <c r="F21" t="n">
+      <c r="C21" s="1">
+        <v>1.8135352581152999E-6</v>
+      </c>
+      <c r="D21" s="2">
+        <v>0.40723905103168401</v>
+      </c>
+      <c r="E21" s="1">
+        <v>1.7357596396060701E-4</v>
+      </c>
+      <c r="F21" s="2">
         <v>0.10599021393048</v>
       </c>
-    </row>
-    <row r="22">
+      <c r="G21" t="s">
+        <v>55</v>
+      </c>
+      <c r="H21" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>25</v>
       </c>
       <c r="B22" t="s">
         <v>50</v>
       </c>
-      <c r="C22" t="n">
-        <v>0.438268552354132</v>
-      </c>
-      <c r="D22" t="n">
-        <v>0.228249503549798</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0.277437392872983</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.824659804854675</v>
-      </c>
-    </row>
-    <row r="23">
+      <c r="C22" s="2">
+        <v>0.43826855235413198</v>
+      </c>
+      <c r="D22" s="2">
+        <v>0.22824950354979801</v>
+      </c>
+      <c r="E22" s="2">
+        <v>0.27743739287298302</v>
+      </c>
+      <c r="F22" s="2">
+        <v>0.82465980485467505</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>26</v>
       </c>
       <c r="B23" t="s">
         <v>51</v>
       </c>
-      <c r="C23" t="n">
-        <v>0.990533619003452</v>
-      </c>
-      <c r="D23" t="n">
-        <v>0.943773832433264</v>
-      </c>
-      <c r="E23" t="n">
-        <v>0.750095762805903</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0.309306177030345</v>
-      </c>
-    </row>
-    <row r="24">
+      <c r="C23" s="2">
+        <v>0.99053361900345205</v>
+      </c>
+      <c r="D23" s="2">
+        <v>0.94377383243326396</v>
+      </c>
+      <c r="E23" s="2">
+        <v>0.75009576280590295</v>
+      </c>
+      <c r="F23" s="2">
+        <v>0.30930617703034502</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>27</v>
       </c>
       <c r="B24" t="s">
         <v>52</v>
       </c>
-      <c r="C24" t="n">
-        <v>0.0430313927599789</v>
-      </c>
-      <c r="D24" t="n">
-        <v>0.0415698007268024</v>
-      </c>
-      <c r="E24" t="n">
-        <v>0.63518477780683</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0.0899376816520633</v>
-      </c>
-    </row>
-    <row r="25">
+      <c r="C24" s="1">
+        <v>4.3031392759978901E-2</v>
+      </c>
+      <c r="D24" s="1">
+        <v>4.15698007268024E-2</v>
+      </c>
+      <c r="E24" s="2">
+        <v>0.63518477780683003</v>
+      </c>
+      <c r="F24" s="2">
+        <v>8.9937681652063298E-2</v>
+      </c>
+      <c r="G24" t="s">
+        <v>55</v>
+      </c>
+      <c r="H24" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>28</v>
       </c>
       <c r="B25" t="s">
         <v>53</v>
       </c>
-      <c r="C25" t="n">
-        <v>0.0368182491656618</v>
-      </c>
-      <c r="D25" t="n">
-        <v>0.686679472665445</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.0713265587131307</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0.646720317868624</v>
-      </c>
-    </row>
-    <row r="26">
+      <c r="C25" s="1">
+        <v>3.6818249165661801E-2</v>
+      </c>
+      <c r="D25" s="2">
+        <v>0.68667947266544505</v>
+      </c>
+      <c r="E25" s="3">
+        <v>7.1326558713130706E-2</v>
+      </c>
+      <c r="F25" s="2">
+        <v>0.64672031786862405</v>
+      </c>
+      <c r="G25" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>29</v>
       </c>
       <c r="B26" t="s">
         <v>54</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C26" s="2">
         <v>0.488653142192496</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D26" s="2">
         <v>0.885867845106311</v>
       </c>
-      <c r="E26" t="n">
-        <v>0.53894019329448</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0.0733522542381077</v>
+      <c r="E26" s="2">
+        <v>0.53894019329447995</v>
+      </c>
+      <c r="F26" s="2">
+        <v>7.3352254238107706E-2</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>